--- a/同位素杂质计算/STD_0.005_验证.xlsx
+++ b/同位素杂质计算/STD_0.005_验证.xlsx
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J3" s="26" t="inlineStr">
         <is>
-          <t>不带电荷分子量</t>
+          <t>不带电荷单同位素质量</t>
         </is>
       </c>
       <c r="K3" s="26" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J3" s="26" t="inlineStr">
         <is>
-          <t>不带电荷分子量</t>
+          <t>不带电荷单同位素质量</t>
         </is>
       </c>
       <c r="K3" s="26" t="inlineStr">
@@ -2494,7 +2494,7 @@
         <v>-5.7</v>
       </c>
       <c r="I12" s="45" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="29" t="n">
         <v>2831.4158</v>
